--- a/tools/misc/product-metadata.xlsx
+++ b/tools/misc/product-metadata.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10104" uniqueCount="4356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10168" uniqueCount="4376">
   <si>
     <t>tsv_path</t>
   </si>
@@ -13084,6 +13084,66 @@
   </si>
   <si>
     <t>REX</t>
+  </si>
+  <si>
+    <t>ce13_jungle_frenzy_cdda</t>
+  </si>
+  <si>
+    <t>ce13_jungle_frenzy_wav</t>
+  </si>
+  <si>
+    <t>ce14_live_bass_grooves_cdda</t>
+  </si>
+  <si>
+    <t>ce14_live_bass_grooves_wav</t>
+  </si>
+  <si>
+    <t>ce15_world_class_breaks_cdda</t>
+  </si>
+  <si>
+    <t>ce15_world_class_breaks_wav</t>
+  </si>
+  <si>
+    <t>ce16_drum_percussion_tools_cdda</t>
+  </si>
+  <si>
+    <t>ce16_drum_percussion_tools_wav</t>
+  </si>
+  <si>
+    <t>Jungle Frenzy</t>
+  </si>
+  <si>
+    <t>Live Bass Grooves</t>
+  </si>
+  <si>
+    <t>World Class Breaks</t>
+  </si>
+  <si>
+    <t>Drum &amp; Percussion Tools</t>
+  </si>
+  <si>
+    <t>/ZERO_G/CREATIVE_ESSENTIALS/13_JUNGLE_FRENZY/CDDA.tsv</t>
+  </si>
+  <si>
+    <t>/ZERO_G/CREATIVE_ESSENTIALS/13_JUNGLE_FRENZY/WAV.tsv</t>
+  </si>
+  <si>
+    <t>/ZERO_G/CREATIVE_ESSENTIALS/14_LIVE_BASS_GROOVES/CDDA.tsv</t>
+  </si>
+  <si>
+    <t>/ZERO_G/CREATIVE_ESSENTIALS/14_LIVE_BASS_GROOVES/WAV.tsv</t>
+  </si>
+  <si>
+    <t>/ZERO_G/CREATIVE_ESSENTIALS/15_WORLD_CLASS_BREAKS/CDDA.tsv</t>
+  </si>
+  <si>
+    <t>/ZERO_G/CREATIVE_ESSENTIALS/15_WORLD_CLASS_BREAKS/WAV.tsv</t>
+  </si>
+  <si>
+    <t>/ZERO_G/CREATIVE_ESSENTIALS/16_DRUM_PERCUSSION_TOOLS/CDDA.tsv</t>
+  </si>
+  <si>
+    <t>/ZERO_G/CREATIVE_ESSENTIALS/16_DRUM_PERCUSSION_TOOLS/WAV.tsv</t>
   </si>
 </sst>
 </file>
@@ -13416,7 +13476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L1433"/>
+  <dimension ref="A1:L1441"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -46153,19 +46213,22 @@
         <v>79</v>
       </c>
       <c r="B1415" s="1" t="s">
-        <v>712</v>
+        <v>4356</v>
       </c>
       <c r="C1415" s="1" t="s">
         <v>2097</v>
       </c>
-      <c r="D1415" s="1" t="s">
-        <v>2778</v>
+      <c r="D1415" t="s">
+        <v>4364</v>
       </c>
       <c r="E1415" s="1" t="s">
-        <v>1522</v>
+        <v>4258</v>
+      </c>
+      <c r="F1415" s="1" t="s">
+        <v>4258</v>
       </c>
       <c r="G1415" s="1" t="s">
-        <v>4202</v>
+        <v>4368</v>
       </c>
       <c r="K1415" s="1" t="s">
         <v>4230</v>
@@ -46176,22 +46239,25 @@
         <v>79</v>
       </c>
       <c r="B1416" s="1" t="s">
-        <v>713</v>
+        <v>4357</v>
       </c>
       <c r="C1416" s="1" t="s">
         <v>2097</v>
       </c>
-      <c r="D1416" s="1" t="s">
-        <v>2779</v>
+      <c r="D1416" t="s">
+        <v>4364</v>
       </c>
       <c r="E1416" s="1" t="s">
-        <v>4258</v>
+        <v>4259</v>
+      </c>
+      <c r="F1416" s="1" t="s">
+        <v>4259</v>
       </c>
       <c r="G1416" s="1" t="s">
-        <v>4203</v>
+        <v>4369</v>
       </c>
       <c r="K1416" s="1" t="s">
-        <v>4256</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="1417" spans="1:11">
@@ -46199,22 +46265,25 @@
         <v>79</v>
       </c>
       <c r="B1417" s="1" t="s">
-        <v>714</v>
+        <v>4358</v>
       </c>
       <c r="C1417" s="1" t="s">
         <v>2097</v>
       </c>
-      <c r="D1417" s="1" t="s">
-        <v>2780</v>
+      <c r="D1417" t="s">
+        <v>4365</v>
       </c>
       <c r="E1417" s="1" t="s">
         <v>4258</v>
       </c>
+      <c r="F1417" s="1" t="s">
+        <v>4258</v>
+      </c>
       <c r="G1417" s="1" t="s">
-        <v>4204</v>
+        <v>4370</v>
       </c>
       <c r="K1417" s="1" t="s">
-        <v>4256</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="1418" spans="1:11">
@@ -46222,19 +46291,22 @@
         <v>79</v>
       </c>
       <c r="B1418" s="1" t="s">
-        <v>715</v>
+        <v>4359</v>
       </c>
       <c r="C1418" s="1" t="s">
         <v>2097</v>
       </c>
-      <c r="D1418" s="1" t="s">
-        <v>2781</v>
+      <c r="D1418" t="s">
+        <v>4365</v>
       </c>
       <c r="E1418" s="1" t="s">
-        <v>4258</v>
+        <v>4259</v>
+      </c>
+      <c r="F1418" s="1" t="s">
+        <v>4259</v>
       </c>
       <c r="G1418" s="1" t="s">
-        <v>4205</v>
+        <v>4371</v>
       </c>
       <c r="K1418" s="1" t="s">
         <v>4230</v>
@@ -46245,19 +46317,22 @@
         <v>79</v>
       </c>
       <c r="B1419" s="1" t="s">
-        <v>716</v>
+        <v>4360</v>
       </c>
       <c r="C1419" s="1" t="s">
         <v>2097</v>
       </c>
-      <c r="D1419" s="1" t="s">
-        <v>2782</v>
+      <c r="D1419" t="s">
+        <v>4366</v>
       </c>
       <c r="E1419" s="1" t="s">
-        <v>4354</v>
+        <v>4258</v>
+      </c>
+      <c r="F1419" s="1" t="s">
+        <v>4258</v>
       </c>
       <c r="G1419" s="1" t="s">
-        <v>4206</v>
+        <v>4372</v>
       </c>
       <c r="K1419" s="1" t="s">
         <v>4230</v>
@@ -46268,22 +46343,22 @@
         <v>79</v>
       </c>
       <c r="B1420" s="1" t="s">
-        <v>717</v>
+        <v>4361</v>
       </c>
       <c r="C1420" s="1" t="s">
         <v>2097</v>
       </c>
-      <c r="D1420" s="1" t="s">
-        <v>2783</v>
+      <c r="D1420" t="s">
+        <v>4366</v>
       </c>
       <c r="E1420" s="1" t="s">
-        <v>1522</v>
+        <v>4259</v>
       </c>
       <c r="F1420" s="1" t="s">
-        <v>1522</v>
+        <v>4259</v>
       </c>
       <c r="G1420" s="1" t="s">
-        <v>4207</v>
+        <v>4373</v>
       </c>
       <c r="K1420" s="1" t="s">
         <v>4230</v>
@@ -46294,13 +46369,13 @@
         <v>79</v>
       </c>
       <c r="B1421" s="1" t="s">
-        <v>718</v>
+        <v>4362</v>
       </c>
       <c r="C1421" s="1" t="s">
         <v>2097</v>
       </c>
-      <c r="D1421" s="1" t="s">
-        <v>2783</v>
+      <c r="D1421" t="s">
+        <v>4367</v>
       </c>
       <c r="E1421" s="1" t="s">
         <v>4258</v>
@@ -46309,7 +46384,7 @@
         <v>4258</v>
       </c>
       <c r="G1421" s="1" t="s">
-        <v>4208</v>
+        <v>4374</v>
       </c>
       <c r="K1421" s="1" t="s">
         <v>4230</v>
@@ -46320,22 +46395,22 @@
         <v>79</v>
       </c>
       <c r="B1422" s="1" t="s">
-        <v>719</v>
+        <v>4363</v>
       </c>
       <c r="C1422" s="1" t="s">
         <v>2097</v>
       </c>
-      <c r="D1422" s="1" t="s">
-        <v>2784</v>
+      <c r="D1422" t="s">
+        <v>4367</v>
       </c>
       <c r="E1422" s="1" t="s">
-        <v>1522</v>
+        <v>4259</v>
       </c>
       <c r="F1422" s="1" t="s">
-        <v>1522</v>
+        <v>4259</v>
       </c>
       <c r="G1422" s="1" t="s">
-        <v>4209</v>
+        <v>4375</v>
       </c>
       <c r="K1422" s="1" t="s">
         <v>4230</v>
@@ -46346,22 +46421,19 @@
         <v>79</v>
       </c>
       <c r="B1423" s="1" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="C1423" s="1" t="s">
         <v>2097</v>
       </c>
       <c r="D1423" s="1" t="s">
-        <v>2784</v>
+        <v>2778</v>
       </c>
       <c r="E1423" s="1" t="s">
-        <v>4298</v>
-      </c>
-      <c r="F1423" s="1" t="s">
-        <v>4298</v>
+        <v>1522</v>
       </c>
       <c r="G1423" s="1" t="s">
-        <v>4210</v>
+        <v>4202</v>
       </c>
       <c r="K1423" s="1" t="s">
         <v>4230</v>
@@ -46372,22 +46444,22 @@
         <v>79</v>
       </c>
       <c r="B1424" s="1" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="C1424" s="1" t="s">
         <v>2097</v>
       </c>
       <c r="D1424" s="1" t="s">
-        <v>2785</v>
-      </c>
-      <c r="F1424" s="1" t="s">
-        <v>4322</v>
+        <v>2779</v>
+      </c>
+      <c r="E1424" s="1" t="s">
+        <v>4258</v>
       </c>
       <c r="G1424" s="1" t="s">
-        <v>4211</v>
+        <v>4203</v>
       </c>
       <c r="K1424" s="1" t="s">
-        <v>4230</v>
+        <v>4256</v>
       </c>
     </row>
     <row r="1425" spans="1:11">
@@ -46395,22 +46467,22 @@
         <v>79</v>
       </c>
       <c r="B1425" s="1" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="C1425" s="1" t="s">
         <v>2097</v>
       </c>
       <c r="D1425" s="1" t="s">
-        <v>2786</v>
+        <v>2780</v>
       </c>
       <c r="E1425" s="1" t="s">
         <v>4258</v>
       </c>
       <c r="G1425" s="1" t="s">
-        <v>4212</v>
+        <v>4204</v>
       </c>
       <c r="K1425" s="1" t="s">
-        <v>4230</v>
+        <v>4256</v>
       </c>
     </row>
     <row r="1426" spans="1:11">
@@ -46418,19 +46490,19 @@
         <v>79</v>
       </c>
       <c r="B1426" s="1" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="C1426" s="1" t="s">
         <v>2097</v>
       </c>
       <c r="D1426" s="1" t="s">
-        <v>2787</v>
+        <v>2781</v>
       </c>
       <c r="E1426" s="1" t="s">
         <v>4258</v>
       </c>
       <c r="G1426" s="1" t="s">
-        <v>4213</v>
+        <v>4205</v>
       </c>
       <c r="K1426" s="1" t="s">
         <v>4230</v>
@@ -46441,22 +46513,19 @@
         <v>79</v>
       </c>
       <c r="B1427" s="1" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="C1427" s="1" t="s">
         <v>2097</v>
       </c>
       <c r="D1427" s="1" t="s">
-        <v>2788</v>
+        <v>2782</v>
       </c>
       <c r="E1427" s="1" t="s">
-        <v>4298</v>
-      </c>
-      <c r="F1427" s="1" t="s">
-        <v>4298</v>
+        <v>4354</v>
       </c>
       <c r="G1427" s="1" t="s">
-        <v>4214</v>
+        <v>4206</v>
       </c>
       <c r="K1427" s="1" t="s">
         <v>4230</v>
@@ -46467,19 +46536,22 @@
         <v>79</v>
       </c>
       <c r="B1428" s="1" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="C1428" s="1" t="s">
         <v>2097</v>
       </c>
       <c r="D1428" s="1" t="s">
-        <v>2789</v>
+        <v>2783</v>
       </c>
       <c r="E1428" s="1" t="s">
-        <v>4258</v>
+        <v>1522</v>
+      </c>
+      <c r="F1428" s="1" t="s">
+        <v>1522</v>
       </c>
       <c r="G1428" s="1" t="s">
-        <v>4215</v>
+        <v>4207</v>
       </c>
       <c r="K1428" s="1" t="s">
         <v>4230</v>
@@ -46490,13 +46562,13 @@
         <v>79</v>
       </c>
       <c r="B1429" s="1" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="C1429" s="1" t="s">
         <v>2097</v>
       </c>
       <c r="D1429" s="1" t="s">
-        <v>2790</v>
+        <v>2783</v>
       </c>
       <c r="E1429" s="1" t="s">
         <v>4258</v>
@@ -46505,7 +46577,7 @@
         <v>4258</v>
       </c>
       <c r="G1429" s="1" t="s">
-        <v>4216</v>
+        <v>4208</v>
       </c>
       <c r="K1429" s="1" t="s">
         <v>4230</v>
@@ -46516,22 +46588,22 @@
         <v>79</v>
       </c>
       <c r="B1430" s="1" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="C1430" s="1" t="s">
         <v>2097</v>
       </c>
       <c r="D1430" s="1" t="s">
-        <v>2790</v>
+        <v>2784</v>
       </c>
       <c r="E1430" s="1" t="s">
-        <v>4259</v>
+        <v>1522</v>
       </c>
       <c r="F1430" s="1" t="s">
-        <v>4259</v>
+        <v>1522</v>
       </c>
       <c r="G1430" s="1" t="s">
-        <v>4217</v>
+        <v>4209</v>
       </c>
       <c r="K1430" s="1" t="s">
         <v>4230</v>
@@ -46542,22 +46614,22 @@
         <v>79</v>
       </c>
       <c r="B1431" s="1" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="C1431" s="1" t="s">
         <v>2097</v>
       </c>
       <c r="D1431" s="1" t="s">
-        <v>2791</v>
+        <v>2784</v>
       </c>
       <c r="E1431" s="1" t="s">
-        <v>4259</v>
+        <v>4298</v>
       </c>
       <c r="F1431" s="1" t="s">
-        <v>4259</v>
+        <v>4298</v>
       </c>
       <c r="G1431" s="1" t="s">
-        <v>4218</v>
+        <v>4210</v>
       </c>
       <c r="K1431" s="1" t="s">
         <v>4230</v>
@@ -46568,22 +46640,19 @@
         <v>79</v>
       </c>
       <c r="B1432" s="1" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="C1432" s="1" t="s">
         <v>2097</v>
       </c>
       <c r="D1432" s="1" t="s">
-        <v>2792</v>
-      </c>
-      <c r="E1432" s="1" t="s">
-        <v>4259</v>
+        <v>2785</v>
       </c>
       <c r="F1432" s="1" t="s">
-        <v>4259</v>
+        <v>4322</v>
       </c>
       <c r="G1432" s="1" t="s">
-        <v>4219</v>
+        <v>4211</v>
       </c>
       <c r="K1432" s="1" t="s">
         <v>4230</v>
@@ -46594,21 +46663,220 @@
         <v>79</v>
       </c>
       <c r="B1433" s="1" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="C1433" s="1" t="s">
         <v>2097</v>
       </c>
       <c r="D1433" s="1" t="s">
+        <v>2786</v>
+      </c>
+      <c r="E1433" s="1" t="s">
+        <v>4258</v>
+      </c>
+      <c r="G1433" s="1" t="s">
+        <v>4212</v>
+      </c>
+      <c r="K1433" s="1" t="s">
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:11">
+      <c r="A1434" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1434" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="C1434" s="1" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D1434" s="1" t="s">
+        <v>2787</v>
+      </c>
+      <c r="E1434" s="1" t="s">
+        <v>4258</v>
+      </c>
+      <c r="G1434" s="1" t="s">
+        <v>4213</v>
+      </c>
+      <c r="K1434" s="1" t="s">
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:11">
+      <c r="A1435" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1435" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="C1435" s="1" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D1435" s="1" t="s">
+        <v>2788</v>
+      </c>
+      <c r="E1435" s="1" t="s">
+        <v>4298</v>
+      </c>
+      <c r="F1435" s="1" t="s">
+        <v>4298</v>
+      </c>
+      <c r="G1435" s="1" t="s">
+        <v>4214</v>
+      </c>
+      <c r="K1435" s="1" t="s">
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:11">
+      <c r="A1436" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1436" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="C1436" s="1" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D1436" s="1" t="s">
+        <v>2789</v>
+      </c>
+      <c r="E1436" s="1" t="s">
+        <v>4258</v>
+      </c>
+      <c r="G1436" s="1" t="s">
+        <v>4215</v>
+      </c>
+      <c r="K1436" s="1" t="s">
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:11">
+      <c r="A1437" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1437" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="C1437" s="1" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D1437" s="1" t="s">
+        <v>2790</v>
+      </c>
+      <c r="E1437" s="1" t="s">
+        <v>4258</v>
+      </c>
+      <c r="F1437" s="1" t="s">
+        <v>4258</v>
+      </c>
+      <c r="G1437" s="1" t="s">
+        <v>4216</v>
+      </c>
+      <c r="K1437" s="1" t="s">
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:11">
+      <c r="A1438" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1438" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="C1438" s="1" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D1438" s="1" t="s">
+        <v>2790</v>
+      </c>
+      <c r="E1438" s="1" t="s">
+        <v>4259</v>
+      </c>
+      <c r="F1438" s="1" t="s">
+        <v>4259</v>
+      </c>
+      <c r="G1438" s="1" t="s">
+        <v>4217</v>
+      </c>
+      <c r="K1438" s="1" t="s">
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:11">
+      <c r="A1439" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1439" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="C1439" s="1" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D1439" s="1" t="s">
+        <v>2791</v>
+      </c>
+      <c r="E1439" s="1" t="s">
+        <v>4259</v>
+      </c>
+      <c r="F1439" s="1" t="s">
+        <v>4259</v>
+      </c>
+      <c r="G1439" s="1" t="s">
+        <v>4218</v>
+      </c>
+      <c r="K1439" s="1" t="s">
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:11">
+      <c r="A1440" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1440" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="C1440" s="1" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D1440" s="1" t="s">
+        <v>2792</v>
+      </c>
+      <c r="E1440" s="1" t="s">
+        <v>4259</v>
+      </c>
+      <c r="F1440" s="1" t="s">
+        <v>4259</v>
+      </c>
+      <c r="G1440" s="1" t="s">
+        <v>4219</v>
+      </c>
+      <c r="K1440" s="1" t="s">
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:11">
+      <c r="A1441" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1441" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="C1441" s="1" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D1441" s="1" t="s">
         <v>2793</v>
       </c>
-      <c r="E1433" s="1" t="s">
+      <c r="E1441" s="1" t="s">
         <v>4355</v>
       </c>
-      <c r="G1433" s="1" t="s">
+      <c r="G1441" s="1" t="s">
         <v>4220</v>
       </c>
-      <c r="K1433" s="1" t="s">
+      <c r="K1441" s="1" t="s">
         <v>4230</v>
       </c>
     </row>
